--- a/Assets/Excels/StageData.xlsx
+++ b/Assets/Excels/StageData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>stagenum</t>
   </si>
@@ -71,13 +71,24 @@
   </si>
   <si>
     <t>WaveIDs</t>
+  </si>
+  <si>
+    <t>1,2,3</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="64" formatCode="@"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <sz val="11.0"/>
@@ -676,7 +687,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -690,6 +701,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="64" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1103,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1116,6 +1130,12 @@
       <c r="C3" s="1">
         <v>1</v>
       </c>
+      <c r="D3" s="1">
+        <v>2</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1">
@@ -1126,6 +1146,12 @@
       </c>
       <c r="C4" s="1">
         <v>2</v>
+      </c>
+      <c r="D4" s="1">
+        <v>2</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -1138,6 +1164,12 @@
       <c r="C5" s="1">
         <v>3</v>
       </c>
+      <c r="D5" s="1">
+        <v>2</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="1">
@@ -1149,6 +1181,12 @@
       <c r="C6" s="1">
         <v>4</v>
       </c>
+      <c r="D6" s="1">
+        <v>2</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="1">
@@ -1160,6 +1198,12 @@
       <c r="C7" s="1">
         <v>5</v>
       </c>
+      <c r="D7" s="1">
+        <v>2</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="1">
@@ -1171,6 +1215,12 @@
       <c r="C8" s="1">
         <v>6</v>
       </c>
+      <c r="D8" s="1">
+        <v>2</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1">
@@ -1182,6 +1232,12 @@
       <c r="C9" s="1">
         <v>1</v>
       </c>
+      <c r="D9" s="1">
+        <v>2</v>
+      </c>
+      <c r="E9" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="1">
@@ -1193,6 +1249,12 @@
       <c r="C10" s="1">
         <v>2</v>
       </c>
+      <c r="D10" s="1">
+        <v>2</v>
+      </c>
+      <c r="E10" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="1">
@@ -1204,6 +1266,12 @@
       <c r="C11" s="1">
         <v>3</v>
       </c>
+      <c r="D11" s="1">
+        <v>2</v>
+      </c>
+      <c r="E11" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="1">
@@ -1215,6 +1283,12 @@
       <c r="C12" s="1">
         <v>4</v>
       </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1">
@@ -1226,6 +1300,12 @@
       <c r="C13" s="1">
         <v>5</v>
       </c>
+      <c r="D13" s="1">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="1">
@@ -1237,6 +1317,12 @@
       <c r="C14" s="1">
         <v>6</v>
       </c>
+      <c r="D14" s="1">
+        <v>2</v>
+      </c>
+      <c r="E14" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1">
@@ -1248,6 +1334,12 @@
       <c r="C15" s="1">
         <v>1</v>
       </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="1">
@@ -1259,8 +1351,14 @@
       <c r="C16" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
+      <c r="D16" s="1">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1270,8 +1368,14 @@
       <c r="C17" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
+      <c r="D17" s="1">
+        <v>2</v>
+      </c>
+      <c r="E17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1281,8 +1385,14 @@
       <c r="C18" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1292,8 +1402,14 @@
       <c r="C19" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
+      <c r="D19" s="1">
+        <v>2</v>
+      </c>
+      <c r="E19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1303,8 +1419,14 @@
       <c r="C20" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
+      <c r="D20" s="1">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1314,8 +1436,14 @@
       <c r="C21" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:3">
+      <c r="D21" s="1">
+        <v>2</v>
+      </c>
+      <c r="E21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1325,8 +1453,14 @@
       <c r="C22" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
+      <c r="D22" s="1">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1336,8 +1470,14 @@
       <c r="C23" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
+      <c r="D23" s="1">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1347,8 +1487,14 @@
       <c r="C24" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:3">
+      <c r="D24" s="1">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1358,8 +1504,14 @@
       <c r="C25" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
+      <c r="D25" s="1">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1369,8 +1521,14 @@
       <c r="C26" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1380,8 +1538,14 @@
       <c r="C27" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
+      <c r="D27" s="1">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1391,8 +1555,14 @@
       <c r="C28" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:3">
+      <c r="D28" s="1">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1402,8 +1572,14 @@
       <c r="C29" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
+      <c r="D29" s="1">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1413,8 +1589,14 @@
       <c r="C30" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:3">
+      <c r="D30" s="1">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1424,8 +1606,14 @@
       <c r="C31" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="32" spans="1:3">
+      <c r="D31" s="1">
+        <v>2</v>
+      </c>
+      <c r="E31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1435,8 +1623,14 @@
       <c r="C32" s="1">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
+      <c r="D32" s="1">
+        <v>2</v>
+      </c>
+      <c r="E32" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -1446,8 +1640,14 @@
       <c r="C33" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:3">
+      <c r="D33" s="1">
+        <v>2</v>
+      </c>
+      <c r="E33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -1457,8 +1657,14 @@
       <c r="C34" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="35" spans="1:3">
+      <c r="D34" s="1">
+        <v>2</v>
+      </c>
+      <c r="E34" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -1468,8 +1674,14 @@
       <c r="C35" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:3">
+      <c r="D35" s="1">
+        <v>2</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" s="1">
         <v>34</v>
       </c>
@@ -1479,8 +1691,14 @@
       <c r="C36" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:3">
+      <c r="D36" s="1">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" s="1">
         <v>35</v>
       </c>
@@ -1490,8 +1708,14 @@
       <c r="C37" s="1">
         <v>5</v>
       </c>
-    </row>
-    <row r="38" spans="1:3">
+      <c r="D37" s="1">
+        <v>2</v>
+      </c>
+      <c r="E37" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -1500,6 +1724,12 @@
       </c>
       <c r="C38" s="1">
         <v>6</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="5">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Excels/StageData.xlsx
+++ b/Assets/Excels/StageData.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>stagenum</t>
   </si>
@@ -80,6 +80,12 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>1,2,5</t>
+  </si>
+  <si>
+    <t>1,3,5</t>
   </si>
 </sst>
 </file>
@@ -1082,8 +1088,11 @@
   <sheetFormatPr defaultColWidth="9.00000000" defaultRowHeight="16.500000"/>
   <cols>
     <col min="1" max="1" style="1" width="5.50500011" customWidth="1" outlineLevel="0"/>
-    <col min="2" max="3" style="1" width="9.88000011" customWidth="1" outlineLevel="0"/>
-    <col min="4" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
+    <col min="2" max="2" style="1" width="9.88000011" customWidth="1" outlineLevel="0"/>
+    <col min="3" max="3" style="1" width="14.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="4" max="4" style="1" width="14.50500011" customWidth="1" outlineLevel="0"/>
+    <col min="5" max="5" style="1" width="12.25500011" customWidth="1" outlineLevel="0"/>
+    <col min="6" max="16384" style="1" width="9.00500011" customWidth="1" outlineLevel="0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" s="2" customFormat="1">
@@ -1131,10 +1140,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:5">

--- a/Assets/Excels/StageData.xlsx
+++ b/Assets/Excels/StageData.xlsx
@@ -42,112 +42,27 @@
     <t>string</t>
   </si>
   <si>
-    <r>
-      <t>1,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4,5</t>
-    </r>
+    <t>1,2,3,4</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>6,7,8,9,10</t>
+    <t>5,6,7,8</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1,12,13,14,15</t>
-    </r>
+    <t>9,10,11,12</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6,17,18,19,20</t>
-    </r>
+    <t>13,14,15,16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1,22,23,24,25</t>
-    </r>
+    <t>17,18,19,20</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>6,27,28,29,30</t>
-    </r>
+    <t>21,22,23,24</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -654,7 +569,7 @@
     <col min="2" max="2" width="9.8984375" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.296875" style="1" customWidth="1"/>
     <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="16.09765625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.19921875" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
